--- a/quellen für wis arbeit.xlsx
+++ b/quellen für wis arbeit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MikhailLeshchenko\strava_plus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{716AF9B2-996C-4F99-A5C1-EE82CC4C8760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52BCA5BB-E3A3-4427-9EC6-924613360894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-1056" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -24,12 +24,141 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+  <si>
+    <t>Zitate</t>
+  </si>
+  <si>
+    <t>Buch</t>
+  </si>
+  <si>
+    <t>Autor</t>
+  </si>
+  <si>
+    <t>Zugriffsdatum</t>
+  </si>
+  <si>
+    <t>Seite</t>
+  </si>
+  <si>
+    <t>Trainingswissenschaft: Ein Lehrbuch in 14 Lektionen</t>
+  </si>
+  <si>
+    <t>Unter der maximalen HF wird jene HF verstanden, die von einem Sportler bei voller subjektiver Ausbelastung erreicht wird. Dabei stellt die Ausbelastung einen Zustand der willensmäßigen Mobilisierung aller Leistungsreserven dar, unter Einsatz größerer Muskelgruppen mit höchstmöglicher Intensität. Die maximale HF kennzeichnet einen Momentzustand des Herz-Kreislauf-Systems und hat keinen Bezug zur Leistungsfähigkeit des Sportlers.</t>
+  </si>
+  <si>
+    <t>Kuno Hottenrott, Georg Neumann</t>
+  </si>
+  <si>
+    <t>Die Herzfrequenz ist eine zentrale Messgröße bei der Beurteilung der Herz-Kreislauf-Funktion in Ruhe und unter Belastung</t>
+  </si>
+  <si>
+    <t>Optimiertes Ausdauertraining</t>
+  </si>
+  <si>
+    <t>Neumann, G., Pfützner, A. &amp; Berbalk, A</t>
+  </si>
+  <si>
+    <t>Die durchschnittliche Herzfrequenz stellt den Mittelwert in einer Trainingseinheit, einem Trainingsabschnitt oder einer akuten Belastungs- beziehungsweise Nachbelastungsphase (akive Erholung) über einen spezifischen Messzeitraum dar.</t>
+  </si>
+  <si>
+    <t>Voll im Takt – Ausdauertraining im Rhythmus des Herzschlags</t>
+  </si>
+  <si>
+    <t>Thomas Gronwald, Alexander Törpel</t>
+  </si>
+  <si>
+    <t>Tristan Hogue</t>
+  </si>
+  <si>
+    <t>COROS-Herzfrequenzzonen: Der ultimative Guide</t>
+  </si>
+  <si>
+    <t>https://coros.com/de/stories/coros-metrics/c/coros-heart-rate-zones-the-ultimate-guide</t>
+  </si>
+  <si>
+    <t>Zweite Pulszone ermöglicht es, Gespräche bequem zu führen. Er eignet sich für das grundlegende kasrdiovaskuläre Training, das hauptsächlich auf aerobe Kapazität abzielt. Diese Intensität kann über mehrere Stunden aufrechterhalten werden.</t>
+  </si>
+  <si>
+    <t>Dritte Pulszone führt zu einem plötzlichen Anstieg der Atemfrequenz und es fällt schwerer, Gespräche zu führen. Er eignet sich zur Verbesserung der Lauftechnik und -form sowie zur Schulung von Atmung und Kadenz.
+Diese Intensität kann für 1–3 Stunden aufrechterhalten werden.</t>
+  </si>
+  <si>
+    <t>Vierte Pulszone ist genau dein Schwellenbereich. Die Anstrengung ist kaum nachhaltig und eher unangenehm. Das Training in dieser Zone verbessert deine Fähigkeit, härtere Anstrengungen länger aufrechtzuerhalten.
+Diese Intensität kann für 45–60 Minuten aufrechterhalten werden.</t>
+  </si>
+  <si>
+    <t>fünfte Pulszone, Hier hast du deinen Schwellenbereich überschritten – und es wird eher unangenehm und nicht mehr nachhaltig. Obwohl es noch nicht dem maximalen Aufwand entspricht, gilt dieser Bereich für hochintensives Training, um hauptsächlich die VO2max-Fähigkeit zu verbessern.
+Diese Intensität kann für 3–7 Minuten aufrechterhalten werden.</t>
+  </si>
+  <si>
+    <t>sechste Pulszone entspricht dem maximalen Einsatz, bei dem dein Körper dich zum Stoppen zwingen wird, bevor du die maximale Kapazität deines Systems erreichst. Er eignet sich zur Verbesserung der neuromuskulären Kapazität und schnelleren Bewegungen.
+Diese Intensität kann weniger als 3 Minuten aufrechterhalten werden.</t>
+  </si>
+  <si>
+    <t>nullte Pulszone entspricht einer sehr geringen Trainingsintensität. Er eignet sich für aktive Erholung. Diese Intesität kann über mehrere Tage aufrehterhalten werden.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Die Trainingsbelastung ist die Menge an physischem </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Stress</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, dem dein Körper durch ein Training ausgesetzt ist.</t>
+    </r>
+  </si>
+  <si>
+    <t>EvoLab-Metriken</t>
+  </si>
+  <si>
+    <t>https://t.coros.com/admin/views/data-analysis</t>
+  </si>
+  <si>
+    <t>n.n.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -52,13 +181,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -337,12 +476,213 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="1" max="1" width="97.140625" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" customWidth="1"/>
+    <col min="3" max="3" width="35.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E4">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="1">
+        <v>46253</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{443E79F9-4ACF-423F-AD65-5F2DE771D856}"/>
+    <hyperlink ref="E6" r:id="rId2" xr:uid="{B391CC90-ED48-4B15-BB7F-DCB2FD9DD8F5}"/>
+    <hyperlink ref="E7" r:id="rId3" xr:uid="{4300DA1C-0FA6-4FF6-B1F7-819F6F2870C5}"/>
+    <hyperlink ref="E8" r:id="rId4" xr:uid="{42997B69-02BA-4CE8-8235-B546BC14029E}"/>
+    <hyperlink ref="E9" r:id="rId5" xr:uid="{E2A304C1-268A-4FB5-AB24-A01A38FDE14C}"/>
+    <hyperlink ref="E10" r:id="rId6" xr:uid="{F10AF3E6-E105-4616-9921-B5B800EBE60A}"/>
+    <hyperlink ref="E11" r:id="rId7" xr:uid="{95DD3513-26C6-4F91-9AA2-013C7842C140}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>